--- a/data/final/input/HoaDon2023_Template.xlsx
+++ b/data/final/input/HoaDon2023_Template.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\as\Development\back_end_projects\java\DaElectric\data\final\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AB5365B-88A4-4106-BCB4-31E7F9EC6E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F318947-D05B-4734-A3B5-611CFF7C219A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{41AB8A55-0524-4A88-A23F-6D1C9F885B49}"/>
   </bookViews>
   <sheets>
-    <sheet name="T10_2024" sheetId="1" r:id="rId1"/>
+    <sheet name="T8_2025" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -114,9 +114,6 @@
     <t>Đơn giá:</t>
   </si>
   <si>
-    <t>Công ghi điện</t>
-  </si>
-  <si>
     <t>Tổng tiền thanh toán:</t>
   </si>
   <si>
@@ -184,7 +181,10 @@
     <t>{{totalPayment}}</t>
   </si>
   <si>
-    <t>Đak Đoa, ngày      tháng      năm 2025</t>
+    <t>Đak Đoa, ngày      tháng      năm 2026</t>
+  </si>
+  <si>
+    <t>Công ghi điện</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1075,7 @@
       <c r="B1" s="12"/>
       <c r="C1" s="1"/>
       <c r="D1" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1" s="13"/>
     </row>
@@ -1084,14 +1084,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -1099,14 +1099,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -1114,14 +1114,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
@@ -1129,14 +1129,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -1144,14 +1144,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
@@ -1159,76 +1159,76 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B8" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E8" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.4" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="85.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="7"/>
       <c r="D10" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="15"/>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="8"/>
       <c r="D11" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="16"/>
     </row>
     <row r="12" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="9"/>
       <c r="D12" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="11"/>
     </row>
